--- a/api/templates/daily-sales-report.xlsx
+++ b/api/templates/daily-sales-report.xlsx
@@ -23310,7 +23310,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFD966"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23328,7 +23328,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -25885,12 +25885,12 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFAAAAAA"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FF505050"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFFFD966"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFB97034"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FFF4B183"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="00800000"/>
       <rgbColor rgb="00008000"/>
       <rgbColor rgb="00000080"/>
